--- a/Document/New REQUIREMENT.xlsx
+++ b/Document/New REQUIREMENT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bilal\ERPRepo\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F91F60E-9D14-40AF-94EE-72713D7C31DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C7E48-2DBA-48CB-B427-41E30F895AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{214A8478-E50A-4AE8-A0BB-51E392BA635B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{214A8478-E50A-4AE8-A0BB-51E392BA635B}"/>
   </bookViews>
   <sheets>
     <sheet name="Ready For Dispatched" sheetId="6" r:id="rId1"/>
@@ -724,8 +724,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{EC4A64F1-B668-4921-B303-148E9D1967A3}" name="Table7" displayName="Table7" ref="A5:J6" totalsRowShown="0">
-  <autoFilter ref="A5:J6" xr:uid="{763B0444-623B-4778-8C6E-12C42E780733}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{EC4A64F1-B668-4921-B303-148E9D1967A3}" name="Table7" displayName="Table7" ref="A6:J7" totalsRowShown="0">
+  <autoFilter ref="A6:J7" xr:uid="{763B0444-623B-4778-8C6E-12C42E780733}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FAAB77C8-1C42-42FA-A041-C5B0F5A75C29}" name="Booking No#"/>
     <tableColumn id="2" xr3:uid="{D29BDB19-F8C2-4DF7-89ED-27900C0084D9}" name="Container No#"/>
@@ -1204,7 +1204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D25DF428-5068-4BA7-8310-10B2A5137995}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
@@ -1224,67 +1224,67 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-    </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>56</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>56</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>56</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G7" t="s">
         <v>56</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H7" t="s">
         <v>56</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I7" t="s">
         <v>56</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J7" t="s">
         <v>90</v>
       </c>
     </row>

--- a/Document/New REQUIREMENT.xlsx
+++ b/Document/New REQUIREMENT.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bilal\ERPRepo\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C7E48-2DBA-48CB-B427-41E30F895AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001DD38-302C-44F7-B7DB-E3865D5D3849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{214A8478-E50A-4AE8-A0BB-51E392BA635B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{214A8478-E50A-4AE8-A0BB-51E392BA635B}"/>
   </bookViews>
   <sheets>
     <sheet name="Ready For Dispatched" sheetId="6" r:id="rId1"/>
     <sheet name="Pre-Dispatched" sheetId="2" r:id="rId2"/>
-    <sheet name="Dispatched" sheetId="1" r:id="rId3"/>
+    <sheet name="Dispatched(Train &amp; Truck)" sheetId="1" r:id="rId3"/>
     <sheet name="InTransact (train)" sheetId="3" r:id="rId4"/>
     <sheet name="ReDispatched (train)" sheetId="4" r:id="rId5"/>
-    <sheet name="Delivery" sheetId="5" r:id="rId6"/>
-    <sheet name="Empty DropOff" sheetId="7" r:id="rId7"/>
+    <sheet name="Delivery(Train &amp; Truck)" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
+    <sheet name="Empty DropOff" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -823,22 +824,22 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{900F3657-9A29-43B9-B9D2-06C34B4B90DC}" name="Table5" displayName="Table5" ref="A6:M7" totalsRowShown="0" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{900F3657-9A29-43B9-B9D2-06C34B4B90DC}" name="Table5" displayName="Table5" ref="A6:M7" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A6:M7" xr:uid="{3C9EFFE7-C814-429F-9F3A-0A1D5D6ED679}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1223B788-450F-4A86-AC0D-33C05B6262A2}" name="Booking No " dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{C520D948-8EC2-4782-BB0D-8817414F32A8}" name="Container No" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{B6239AD2-491F-4CCF-BC42-1A0EE35FA49E}" name="Container Size" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{C225B7CD-364A-423E-92F0-234BEDAC6646}" name="Arrival Date" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{06BEACDB-9ABA-46D4-9C33-F378BD44A593}" name="Last Date of Empty Return" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{99C0A979-0EB3-43BC-B8E6-AB4C2B2E3B4D}" name="Delievery Location" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{1EECD11A-B173-4B61-9884-4DF638E2E40C}" name="Vehicle No#" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{6388667F-30B1-40D8-9112-148F6F6FD94A}" name="ReDispatched Datetime" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{E51CB75D-D315-4F48-BF96-456199344FC9}" name="Transpoter Name" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{52768714-0831-4351-BAE5-FAFE66E14F6B}" name="Bilty Number" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{AB343D34-E079-4424-ACDE-296924F6256D}" name="Transportation Cost" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{545F9935-436F-42F5-BBE0-4127FFC48375}" name="Empty DropOff Location" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{D833E3A4-C9F6-48DB-828F-31755484746B}" name="Action" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{1223B788-450F-4A86-AC0D-33C05B6262A2}" name="Booking No " dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{C520D948-8EC2-4782-BB0D-8817414F32A8}" name="Container No" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B6239AD2-491F-4CCF-BC42-1A0EE35FA49E}" name="Container Size" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{C225B7CD-364A-423E-92F0-234BEDAC6646}" name="Arrival Date" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{06BEACDB-9ABA-46D4-9C33-F378BD44A593}" name="Last Date of Empty Return" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{99C0A979-0EB3-43BC-B8E6-AB4C2B2E3B4D}" name="Delievery Location" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{1EECD11A-B173-4B61-9884-4DF638E2E40C}" name="Vehicle No#" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{6388667F-30B1-40D8-9112-148F6F6FD94A}" name="ReDispatched Datetime" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{E51CB75D-D315-4F48-BF96-456199344FC9}" name="Transpoter Name" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{52768714-0831-4351-BAE5-FAFE66E14F6B}" name="Bilty Number" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{AB343D34-E079-4424-ACDE-296924F6256D}" name="Transportation Cost" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{545F9935-436F-42F5-BBE0-4127FFC48375}" name="Empty DropOff Location" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{D833E3A4-C9F6-48DB-828F-31755484746B}" name="Action" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -880,7 +881,7 @@
     <tableColumn id="9" xr3:uid="{96740D8D-6016-49E5-8ABA-94EF7B236795}" name="  Train ID"/>
     <tableColumn id="4" xr3:uid="{8AD0AE71-DB99-45DA-8DD8-554B389DB3CB}" name="Dispatched Date"/>
     <tableColumn id="5" xr3:uid="{0BA2906C-0E6A-4E8E-8442-F4C32B36C37E}" name="Delivery Location"/>
-    <tableColumn id="6" xr3:uid="{98989054-F512-41A3-83F1-5F9A019C6E87}" name="Vehicle No#" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{98989054-F512-41A3-83F1-5F9A019C6E87}" name="Vehicle No#" dataDxfId="14"/>
     <tableColumn id="8" xr3:uid="{D6DE08BA-64B3-4CCA-8898-1F37EBE5D353}" name="Arrival Date at Delivery  "/>
     <tableColumn id="7" xr3:uid="{24B73450-C43A-407B-92EF-2DFBDEF89A16}" name="Delivery Date"/>
     <tableColumn id="10" xr3:uid="{AAE580FA-1653-4B06-A03F-DDEAA9A2BD98}" name="Empty DropOff Location"/>
@@ -2060,6 +2061,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F81D1ED-8B96-4B6F-AD26-0CB3A6A967CB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD1A1F0-BC68-47DE-A65E-DFAE50A57A1E}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Document/New REQUIREMENT.xlsx
+++ b/Document/New REQUIREMENT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bilal\ERPRepo\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001DD38-302C-44F7-B7DB-E3865D5D3849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA65F6F8-2E2E-4A12-A394-D4F095117B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{214A8478-E50A-4AE8-A0BB-51E392BA635B}"/>
+    <workbookView minimized="1" xWindow="3108" yWindow="3012" windowWidth="19932" windowHeight="9348" firstSheet="3" activeTab="5" xr2:uid="{214A8478-E50A-4AE8-A0BB-51E392BA635B}"/>
   </bookViews>
   <sheets>
     <sheet name="Ready For Dispatched" sheetId="6" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="InTransact (train)" sheetId="3" r:id="rId4"/>
     <sheet name="ReDispatched (train)" sheetId="4" r:id="rId5"/>
     <sheet name="Delivery(Train &amp; Truck)" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
-    <sheet name="Empty DropOff" sheetId="7" r:id="rId8"/>
+    <sheet name="Empty DropOff" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>Dispatched</t>
   </si>
@@ -315,6 +314,9 @@
   </si>
   <si>
     <t>Save &amp; Ready For Dispatched</t>
+  </si>
+  <si>
+    <t>auto pcik from dispatched</t>
   </si>
 </sst>
 </file>
@@ -824,22 +826,22 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{900F3657-9A29-43B9-B9D2-06C34B4B90DC}" name="Table5" displayName="Table5" ref="A6:M7" totalsRowShown="0" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{900F3657-9A29-43B9-B9D2-06C34B4B90DC}" name="Table5" displayName="Table5" ref="A6:M7" totalsRowShown="0" dataDxfId="14">
   <autoFilter ref="A6:M7" xr:uid="{3C9EFFE7-C814-429F-9F3A-0A1D5D6ED679}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1223B788-450F-4A86-AC0D-33C05B6262A2}" name="Booking No " dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{C520D948-8EC2-4782-BB0D-8817414F32A8}" name="Container No" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B6239AD2-491F-4CCF-BC42-1A0EE35FA49E}" name="Container Size" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{C225B7CD-364A-423E-92F0-234BEDAC6646}" name="Arrival Date" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{06BEACDB-9ABA-46D4-9C33-F378BD44A593}" name="Last Date of Empty Return" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{99C0A979-0EB3-43BC-B8E6-AB4C2B2E3B4D}" name="Delievery Location" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{1EECD11A-B173-4B61-9884-4DF638E2E40C}" name="Vehicle No#" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{6388667F-30B1-40D8-9112-148F6F6FD94A}" name="ReDispatched Datetime" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{E51CB75D-D315-4F48-BF96-456199344FC9}" name="Transpoter Name" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{52768714-0831-4351-BAE5-FAFE66E14F6B}" name="Bilty Number" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{AB343D34-E079-4424-ACDE-296924F6256D}" name="Transportation Cost" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{545F9935-436F-42F5-BBE0-4127FFC48375}" name="Empty DropOff Location" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{D833E3A4-C9F6-48DB-828F-31755484746B}" name="Action" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{1223B788-450F-4A86-AC0D-33C05B6262A2}" name="Booking No " dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{C520D948-8EC2-4782-BB0D-8817414F32A8}" name="Container No" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{B6239AD2-491F-4CCF-BC42-1A0EE35FA49E}" name="Container Size" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{C225B7CD-364A-423E-92F0-234BEDAC6646}" name="Arrival Date" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{06BEACDB-9ABA-46D4-9C33-F378BD44A593}" name="Last Date of Empty Return" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{99C0A979-0EB3-43BC-B8E6-AB4C2B2E3B4D}" name="Delievery Location" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{1EECD11A-B173-4B61-9884-4DF638E2E40C}" name="Vehicle No#" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{6388667F-30B1-40D8-9112-148F6F6FD94A}" name="ReDispatched Datetime" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{E51CB75D-D315-4F48-BF96-456199344FC9}" name="Transpoter Name" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{52768714-0831-4351-BAE5-FAFE66E14F6B}" name="Bilty Number" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{AB343D34-E079-4424-ACDE-296924F6256D}" name="Transportation Cost" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{545F9935-436F-42F5-BBE0-4127FFC48375}" name="Empty DropOff Location" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{D833E3A4-C9F6-48DB-828F-31755484746B}" name="Action" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -881,7 +883,7 @@
     <tableColumn id="9" xr3:uid="{96740D8D-6016-49E5-8ABA-94EF7B236795}" name="  Train ID"/>
     <tableColumn id="4" xr3:uid="{8AD0AE71-DB99-45DA-8DD8-554B389DB3CB}" name="Dispatched Date"/>
     <tableColumn id="5" xr3:uid="{0BA2906C-0E6A-4E8E-8442-F4C32B36C37E}" name="Delivery Location"/>
-    <tableColumn id="6" xr3:uid="{98989054-F512-41A3-83F1-5F9A019C6E87}" name="Vehicle No#" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{98989054-F512-41A3-83F1-5F9A019C6E87}" name="Vehicle No#" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{D6DE08BA-64B3-4CCA-8898-1F37EBE5D353}" name="Arrival Date at Delivery  "/>
     <tableColumn id="7" xr3:uid="{24B73450-C43A-407B-92EF-2DFBDEF89A16}" name="Delivery Date"/>
     <tableColumn id="10" xr3:uid="{AAE580FA-1653-4B06-A03F-DDEAA9A2BD98}" name="Empty DropOff Location"/>
@@ -1628,7 +1630,7 @@
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1692,7 +1694,7 @@
         <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -2061,15 +2063,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F81D1ED-8B96-4B6F-AD26-0CB3A6A967CB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD1A1F0-BC68-47DE-A65E-DFAE50A57A1E}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
